--- a/data/raw/indicadores_kawak.xlsx
+++ b/data/raw/indicadores_kawak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755A2398-2785-499A-B1D4-49013237F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{755A2398-2785-499A-B1D4-49013237F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA912791-97B7-4995-B1A7-F6B56D77DD81}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10248,6 +10248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y696"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -10328,7 +10329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>77</v>
       </c>
@@ -10390,7 +10391,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>121</v>
       </c>
@@ -10452,7 +10453,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>122</v>
       </c>
@@ -10517,7 +10518,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>124</v>
       </c>
@@ -10582,7 +10583,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>125</v>
       </c>
@@ -10647,7 +10648,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>128</v>
       </c>
@@ -10712,7 +10713,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>172</v>
       </c>
@@ -10774,7 +10775,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>208</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>214</v>
       </c>
@@ -10886,7 +10887,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>218</v>
       </c>
@@ -10942,7 +10943,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>225</v>
       </c>
@@ -10998,7 +10999,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>239</v>
       </c>
@@ -11039,7 +11040,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>436</v>
       </c>
@@ -11104,7 +11105,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>488</v>
       </c>
@@ -11154,7 +11155,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>77</v>
       </c>
@@ -11216,7 +11217,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>121</v>
       </c>
@@ -11281,7 +11282,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>122</v>
       </c>
@@ -11343,7 +11344,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>124</v>
       </c>
@@ -11408,7 +11409,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>125</v>
       </c>
@@ -11473,7 +11474,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>128</v>
       </c>
@@ -11538,7 +11539,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>172</v>
       </c>
@@ -11600,7 +11601,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>208</v>
       </c>
@@ -11665,7 +11666,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>214</v>
       </c>
@@ -11730,7 +11731,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>217</v>
       </c>
@@ -11795,7 +11796,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>218</v>
       </c>
@@ -11860,7 +11861,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>225</v>
       </c>
@@ -11925,7 +11926,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>239</v>
       </c>
@@ -11972,7 +11973,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>241</v>
       </c>
@@ -12034,7 +12035,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>434</v>
       </c>
@@ -12099,7 +12100,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>436</v>
       </c>
@@ -12164,7 +12165,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>485</v>
       </c>
@@ -12226,7 +12227,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>488</v>
       </c>
@@ -12291,7 +12292,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>509</v>
       </c>
@@ -12350,7 +12351,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>77</v>
       </c>
@@ -12412,7 +12413,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>121</v>
       </c>
@@ -12477,7 +12478,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>122</v>
       </c>
@@ -12542,7 +12543,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>124</v>
       </c>
@@ -12607,7 +12608,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>125</v>
       </c>
@@ -12672,7 +12673,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>128</v>
       </c>
@@ -12737,7 +12738,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>172</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>208</v>
       </c>
@@ -12861,7 +12862,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>214</v>
       </c>
@@ -12926,7 +12927,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>217</v>
       </c>
@@ -12991,7 +12992,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>218</v>
       </c>
@@ -13056,7 +13057,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>225</v>
       </c>
@@ -13121,7 +13122,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>239</v>
       </c>
@@ -13168,7 +13169,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>241</v>
       </c>
@@ -13230,7 +13231,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>434</v>
       </c>
@@ -13295,7 +13296,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>436</v>
       </c>
@@ -13360,7 +13361,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>485</v>
       </c>
@@ -13422,7 +13423,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>488</v>
       </c>
@@ -13487,7 +13488,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>509</v>
       </c>
@@ -13543,7 +13544,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>290</v>
       </c>
@@ -13608,7 +13609,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>529</v>
       </c>
@@ -13652,7 +13653,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>77</v>
       </c>
@@ -13714,7 +13715,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>121</v>
       </c>
@@ -13779,7 +13780,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>122</v>
       </c>
@@ -13841,7 +13842,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>124</v>
       </c>
@@ -13906,7 +13907,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>125</v>
       </c>
@@ -13971,7 +13972,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>128</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>172</v>
       </c>
@@ -14098,7 +14099,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>208</v>
       </c>
@@ -14163,7 +14164,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>214</v>
       </c>
@@ -14228,7 +14229,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>217</v>
       </c>
@@ -14293,7 +14294,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>218</v>
       </c>
@@ -14358,7 +14359,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>225</v>
       </c>
@@ -14423,7 +14424,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>239</v>
       </c>
@@ -14473,7 +14474,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>241</v>
       </c>
@@ -14535,7 +14536,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>434</v>
       </c>
@@ -14600,7 +14601,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>436</v>
       </c>
@@ -14665,7 +14666,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>485</v>
       </c>
@@ -14727,7 +14728,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>488</v>
       </c>
@@ -14789,7 +14790,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>509</v>
       </c>
@@ -14845,7 +14846,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>69</v>
       </c>
@@ -14910,7 +14911,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>111</v>
       </c>
@@ -14972,7 +14973,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>197</v>
       </c>
@@ -15034,7 +15035,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>213</v>
       </c>
@@ -15099,7 +15100,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>233</v>
       </c>
@@ -15161,7 +15162,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>234</v>
       </c>
@@ -15223,7 +15224,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>238</v>
       </c>
@@ -15288,7 +15289,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>240</v>
       </c>
@@ -15350,7 +15351,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>251</v>
       </c>
@@ -15412,7 +15413,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>254</v>
       </c>
@@ -15474,7 +15475,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>263</v>
       </c>
@@ -15536,7 +15537,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>265</v>
       </c>
@@ -15598,7 +15599,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>266</v>
       </c>
@@ -15660,7 +15661,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>300</v>
       </c>
@@ -15725,7 +15726,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>301</v>
       </c>
@@ -15790,7 +15791,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>306</v>
       </c>
@@ -15852,7 +15853,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>347</v>
       </c>
@@ -15917,7 +15918,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>348</v>
       </c>
@@ -15979,7 +15980,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>351</v>
       </c>
@@ -16044,7 +16045,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>352</v>
       </c>
@@ -16109,7 +16110,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>368</v>
       </c>
@@ -16171,7 +16172,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>372</v>
       </c>
@@ -16233,7 +16234,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>373</v>
       </c>
@@ -16292,7 +16293,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>390</v>
       </c>
@@ -16357,7 +16358,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>394</v>
       </c>
@@ -16419,7 +16420,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>395</v>
       </c>
@@ -16481,7 +16482,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>409</v>
       </c>
@@ -16543,7 +16544,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>414</v>
       </c>
@@ -16605,7 +16606,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>415</v>
       </c>
@@ -16667,7 +16668,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>416</v>
       </c>
@@ -16729,7 +16730,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>417</v>
       </c>
@@ -16791,7 +16792,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>418</v>
       </c>
@@ -16850,7 +16851,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>420</v>
       </c>
@@ -16909,7 +16910,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>431</v>
       </c>
@@ -16971,7 +16972,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>432</v>
       </c>
@@ -17030,7 +17031,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>453</v>
       </c>
@@ -17092,7 +17093,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>455</v>
       </c>
@@ -17154,7 +17155,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>456</v>
       </c>
@@ -17216,7 +17217,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>457</v>
       </c>
@@ -17278,7 +17279,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>469</v>
       </c>
@@ -17340,7 +17341,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>470</v>
       </c>
@@ -17402,7 +17403,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>471</v>
       </c>
@@ -17464,7 +17465,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>484</v>
       </c>
@@ -17526,7 +17527,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>510</v>
       </c>
@@ -17576,7 +17577,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>511</v>
       </c>
@@ -17626,7 +17627,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>513</v>
       </c>
@@ -17676,7 +17677,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>518</v>
       </c>
@@ -17738,7 +17739,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>529</v>
       </c>
@@ -17782,7 +17783,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>77</v>
       </c>
@@ -17844,7 +17845,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>121</v>
       </c>
@@ -17909,7 +17910,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>122</v>
       </c>
@@ -17974,7 +17975,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>124</v>
       </c>
@@ -18039,7 +18040,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>125</v>
       </c>
@@ -18104,7 +18105,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>128</v>
       </c>
@@ -18169,7 +18170,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>172</v>
       </c>
@@ -18231,7 +18232,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>208</v>
       </c>
@@ -18296,7 +18297,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>214</v>
       </c>
@@ -18361,7 +18362,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>217</v>
       </c>
@@ -18426,7 +18427,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>218</v>
       </c>
@@ -18491,7 +18492,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>225</v>
       </c>
@@ -18556,7 +18557,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>239</v>
       </c>
@@ -18606,7 +18607,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>241</v>
       </c>
@@ -18668,7 +18669,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>434</v>
       </c>
@@ -18733,7 +18734,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>436</v>
       </c>
@@ -18798,7 +18799,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>485</v>
       </c>
@@ -18860,7 +18861,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>488</v>
       </c>
@@ -18925,7 +18926,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>509</v>
       </c>
@@ -18981,7 +18982,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>290</v>
       </c>
@@ -19046,7 +19047,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>529</v>
       </c>
@@ -19090,7 +19091,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>77</v>
       </c>
@@ -19152,7 +19153,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>121</v>
       </c>
@@ -19217,7 +19218,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>122</v>
       </c>
@@ -19279,7 +19280,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>124</v>
       </c>
@@ -19344,7 +19345,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>125</v>
       </c>
@@ -19409,7 +19410,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>128</v>
       </c>
@@ -19474,7 +19475,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>172</v>
       </c>
@@ -19536,7 +19537,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>208</v>
       </c>
@@ -19601,7 +19602,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>214</v>
       </c>
@@ -19666,7 +19667,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>217</v>
       </c>
@@ -19731,7 +19732,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>218</v>
       </c>
@@ -19796,7 +19797,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>225</v>
       </c>
@@ -19861,7 +19862,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>239</v>
       </c>
@@ -19911,7 +19912,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>241</v>
       </c>
@@ -19973,7 +19974,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>434</v>
       </c>
@@ -20038,7 +20039,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>436</v>
       </c>
@@ -20103,7 +20104,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>485</v>
       </c>
@@ -20165,7 +20166,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>488</v>
       </c>
@@ -20230,7 +20231,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>509</v>
       </c>
@@ -20286,7 +20287,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>77</v>
       </c>
@@ -20348,7 +20349,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>121</v>
       </c>
@@ -20413,7 +20414,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>122</v>
       </c>
@@ -20478,7 +20479,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>124</v>
       </c>
@@ -20543,7 +20544,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>125</v>
       </c>
@@ -20608,7 +20609,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>128</v>
       </c>
@@ -20673,7 +20674,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>172</v>
       </c>
@@ -20735,7 +20736,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>208</v>
       </c>
@@ -20800,7 +20801,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -20865,7 +20866,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>217</v>
       </c>
@@ -20930,7 +20931,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>218</v>
       </c>
@@ -20995,7 +20996,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>225</v>
       </c>
@@ -21060,7 +21061,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>239</v>
       </c>
@@ -21110,7 +21111,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>241</v>
       </c>
@@ -21172,7 +21173,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>434</v>
       </c>
@@ -21237,7 +21238,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>436</v>
       </c>
@@ -21302,7 +21303,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>485</v>
       </c>
@@ -21364,7 +21365,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>488</v>
       </c>
@@ -21429,7 +21430,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>509</v>
       </c>
@@ -21488,7 +21489,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>68</v>
       </c>
@@ -21553,7 +21554,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>73</v>
       </c>
@@ -21615,7 +21616,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>74</v>
       </c>
@@ -21677,7 +21678,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>86</v>
       </c>
@@ -21739,7 +21740,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>95</v>
       </c>
@@ -21801,7 +21802,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>143</v>
       </c>
@@ -21863,7 +21864,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>145</v>
       </c>
@@ -21925,7 +21926,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>146</v>
       </c>
@@ -21987,7 +21988,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>148</v>
       </c>
@@ -22049,7 +22050,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>159</v>
       </c>
@@ -22111,7 +22112,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>167</v>
       </c>
@@ -22173,7 +22174,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>193</v>
       </c>
@@ -22235,7 +22236,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>199</v>
       </c>
@@ -22297,7 +22298,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>203</v>
       </c>
@@ -22362,7 +22363,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>204</v>
       </c>
@@ -22427,7 +22428,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>205</v>
       </c>
@@ -22489,7 +22490,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>207</v>
       </c>
@@ -22554,7 +22555,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>215</v>
       </c>
@@ -22619,7 +22620,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>219</v>
       </c>
@@ -22684,7 +22685,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>220</v>
       </c>
@@ -22749,7 +22750,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>230</v>
       </c>
@@ -22814,7 +22815,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>231</v>
       </c>
@@ -22876,7 +22877,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>232</v>
       </c>
@@ -22938,7 +22939,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>245</v>
       </c>
@@ -23000,7 +23001,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>246</v>
       </c>
@@ -23062,7 +23063,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>252</v>
       </c>
@@ -23124,7 +23125,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>256</v>
       </c>
@@ -23186,7 +23187,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>260</v>
       </c>
@@ -23251,7 +23252,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>261</v>
       </c>
@@ -23316,7 +23317,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>262</v>
       </c>
@@ -23381,7 +23382,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>268</v>
       </c>
@@ -23431,7 +23432,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>269</v>
       </c>
@@ -23481,7 +23482,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>270</v>
       </c>
@@ -23531,7 +23532,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>271</v>
       </c>
@@ -23581,7 +23582,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>273</v>
       </c>
@@ -23646,7 +23647,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>274</v>
       </c>
@@ -23708,7 +23709,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>275</v>
       </c>
@@ -23770,7 +23771,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>276</v>
       </c>
@@ -23835,7 +23836,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>277</v>
       </c>
@@ -23900,7 +23901,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>278</v>
       </c>
@@ -23950,7 +23951,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>282</v>
       </c>
@@ -24012,7 +24013,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>283</v>
       </c>
@@ -24074,7 +24075,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>285</v>
       </c>
@@ -24136,7 +24137,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>286</v>
       </c>
@@ -24186,7 +24187,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>292</v>
       </c>
@@ -24248,7 +24249,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>294</v>
       </c>
@@ -24310,7 +24311,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>302</v>
       </c>
@@ -24360,7 +24361,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>303</v>
       </c>
@@ -24422,7 +24423,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>304</v>
       </c>
@@ -24484,7 +24485,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>323</v>
       </c>
@@ -24546,7 +24547,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>324</v>
       </c>
@@ -24608,7 +24609,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>325</v>
       </c>
@@ -24658,7 +24659,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>327</v>
       </c>
@@ -24720,7 +24721,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>332</v>
       </c>
@@ -24785,7 +24786,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>337</v>
       </c>
@@ -24847,7 +24848,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>338</v>
       </c>
@@ -24909,7 +24910,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>341</v>
       </c>
@@ -24971,7 +24972,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>344</v>
       </c>
@@ -25033,7 +25034,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>356</v>
       </c>
@@ -25098,7 +25099,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>357</v>
       </c>
@@ -25148,7 +25149,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>358</v>
       </c>
@@ -25210,7 +25211,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>359</v>
       </c>
@@ -25272,7 +25273,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>362</v>
       </c>
@@ -25334,7 +25335,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>363</v>
       </c>
@@ -25396,7 +25397,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>364</v>
       </c>
@@ -25458,7 +25459,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>369</v>
       </c>
@@ -25520,7 +25521,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>371</v>
       </c>
@@ -25582,7 +25583,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>375</v>
       </c>
@@ -25644,7 +25645,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>376</v>
       </c>
@@ -25709,7 +25710,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>379</v>
       </c>
@@ -25771,7 +25772,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>381</v>
       </c>
@@ -25836,7 +25837,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>382</v>
       </c>
@@ -25901,7 +25902,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>383</v>
       </c>
@@ -25966,7 +25967,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>384</v>
       </c>
@@ -26031,7 +26032,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>385</v>
       </c>
@@ -26096,7 +26097,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>386</v>
       </c>
@@ -26161,7 +26162,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>389</v>
       </c>
@@ -26205,7 +26206,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>397</v>
       </c>
@@ -26267,7 +26268,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>398</v>
       </c>
@@ -26329,7 +26330,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>399</v>
       </c>
@@ -26391,7 +26392,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>400</v>
       </c>
@@ -26453,7 +26454,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>401</v>
       </c>
@@ -26515,7 +26516,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>403</v>
       </c>
@@ -26565,7 +26566,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>408</v>
       </c>
@@ -26627,7 +26628,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>422</v>
       </c>
@@ -26689,7 +26690,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>427</v>
       </c>
@@ -26754,7 +26755,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>428</v>
       </c>
@@ -26819,7 +26820,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>429</v>
       </c>
@@ -26884,7 +26885,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>430</v>
       </c>
@@ -26949,7 +26950,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>433</v>
       </c>
@@ -27014,7 +27015,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>435</v>
       </c>
@@ -27079,7 +27080,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>439</v>
       </c>
@@ -27141,7 +27142,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>440</v>
       </c>
@@ -27203,7 +27204,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>444</v>
       </c>
@@ -27268,7 +27269,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>445</v>
       </c>
@@ -27330,7 +27331,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>447</v>
       </c>
@@ -27392,7 +27393,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>448</v>
       </c>
@@ -27454,7 +27455,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>451</v>
       </c>
@@ -27516,7 +27517,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>452</v>
       </c>
@@ -27572,7 +27573,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>466</v>
       </c>
@@ -27634,7 +27635,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>467</v>
       </c>
@@ -27696,7 +27697,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>468</v>
       </c>
@@ -27823,7 +27824,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>474</v>
       </c>
@@ -27867,7 +27868,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>475</v>
       </c>
@@ -27991,7 +27992,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>477</v>
       </c>
@@ -28032,7 +28033,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>478</v>
       </c>
@@ -28076,7 +28077,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>479</v>
       </c>
@@ -28129,7 +28130,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>480</v>
       </c>
@@ -28238,7 +28239,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>486</v>
       </c>
@@ -28288,7 +28289,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>506</v>
       </c>
@@ -28350,7 +28351,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>507</v>
       </c>
@@ -28412,7 +28413,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>514</v>
       </c>
@@ -28474,7 +28475,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>519</v>
       </c>
@@ -28536,7 +28537,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>523</v>
       </c>
@@ -28601,7 +28602,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>524</v>
       </c>
@@ -28663,7 +28664,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>532</v>
       </c>
@@ -28725,7 +28726,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>533</v>
       </c>
@@ -28787,7 +28788,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>534</v>
       </c>
@@ -28849,7 +28850,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>535</v>
       </c>
@@ -28911,7 +28912,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>536</v>
       </c>
@@ -28973,7 +28974,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>537</v>
       </c>
@@ -29035,7 +29036,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>540</v>
       </c>
@@ -29097,7 +29098,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>543</v>
       </c>
@@ -29147,7 +29148,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>544</v>
       </c>
@@ -29209,7 +29210,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>550</v>
       </c>
@@ -29268,7 +29269,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>551</v>
       </c>
@@ -29327,7 +29328,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>552</v>
       </c>
@@ -29389,7 +29390,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>290</v>
       </c>
@@ -29454,7 +29455,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>69</v>
       </c>
@@ -29519,7 +29520,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>111</v>
       </c>
@@ -29581,7 +29582,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>197</v>
       </c>
@@ -29643,7 +29644,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>213</v>
       </c>
@@ -29708,7 +29709,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>233</v>
       </c>
@@ -29770,7 +29771,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>234</v>
       </c>
@@ -29832,7 +29833,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>238</v>
       </c>
@@ -29897,7 +29898,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>240</v>
       </c>
@@ -29959,7 +29960,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>251</v>
       </c>
@@ -30021,7 +30022,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>254</v>
       </c>
@@ -30083,7 +30084,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>263</v>
       </c>
@@ -30145,7 +30146,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>265</v>
       </c>
@@ -30207,7 +30208,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>266</v>
       </c>
@@ -30269,7 +30270,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>300</v>
       </c>
@@ -30334,7 +30335,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>301</v>
       </c>
@@ -30399,7 +30400,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>306</v>
       </c>
@@ -30464,7 +30465,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>347</v>
       </c>
@@ -30529,7 +30530,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>348</v>
       </c>
@@ -30591,7 +30592,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>351</v>
       </c>
@@ -30656,7 +30657,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>352</v>
       </c>
@@ -30721,7 +30722,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>368</v>
       </c>
@@ -30783,7 +30784,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>372</v>
       </c>
@@ -30845,7 +30846,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>373</v>
       </c>
@@ -30904,7 +30905,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>390</v>
       </c>
@@ -30966,7 +30967,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>394</v>
       </c>
@@ -31028,7 +31029,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>395</v>
       </c>
@@ -31090,7 +31091,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>409</v>
       </c>
@@ -31143,7 +31144,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>414</v>
       </c>
@@ -31202,7 +31203,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>415</v>
       </c>
@@ -31261,7 +31262,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>416</v>
       </c>
@@ -31320,7 +31321,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>417</v>
       </c>
@@ -31379,7 +31380,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>418</v>
       </c>
@@ -31438,7 +31439,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>420</v>
       </c>
@@ -31497,7 +31498,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>431</v>
       </c>
@@ -31559,7 +31560,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>432</v>
       </c>
@@ -31618,7 +31619,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>453</v>
       </c>
@@ -31680,7 +31681,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>455</v>
       </c>
@@ -31742,7 +31743,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>456</v>
       </c>
@@ -31804,7 +31805,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>457</v>
       </c>
@@ -31866,7 +31867,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>469</v>
       </c>
@@ -31925,7 +31926,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>470</v>
       </c>
@@ -31984,7 +31985,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>471</v>
       </c>
@@ -32043,7 +32044,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>484</v>
       </c>
@@ -32105,7 +32106,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>510</v>
       </c>
@@ -32155,7 +32156,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>511</v>
       </c>
@@ -32205,7 +32206,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>513</v>
       </c>
@@ -32255,7 +32256,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>518</v>
       </c>
@@ -32317,7 +32318,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>526</v>
       </c>
@@ -32379,7 +32380,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>526</v>
       </c>
@@ -32441,7 +32442,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>529</v>
       </c>
@@ -32485,7 +32486,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>529</v>
       </c>
@@ -32529,7 +32530,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>288</v>
       </c>
@@ -32591,7 +32592,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>528</v>
       </c>
@@ -32653,7 +32654,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>77</v>
       </c>
@@ -32715,7 +32716,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>121</v>
       </c>
@@ -32780,7 +32781,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>122</v>
       </c>
@@ -32845,7 +32846,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>124</v>
       </c>
@@ -32910,7 +32911,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>125</v>
       </c>
@@ -32975,7 +32976,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>128</v>
       </c>
@@ -33040,7 +33041,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>172</v>
       </c>
@@ -33102,7 +33103,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>208</v>
       </c>
@@ -33167,7 +33168,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>214</v>
       </c>
@@ -33232,7 +33233,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>217</v>
       </c>
@@ -33297,7 +33298,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>218</v>
       </c>
@@ -33362,7 +33363,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>225</v>
       </c>
@@ -33427,7 +33428,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>239</v>
       </c>
@@ -33477,7 +33478,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>241</v>
       </c>
@@ -33539,7 +33540,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>434</v>
       </c>
@@ -33604,7 +33605,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>436</v>
       </c>
@@ -33669,7 +33670,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>485</v>
       </c>
@@ -33731,7 +33732,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>488</v>
       </c>
@@ -33796,7 +33797,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>509</v>
       </c>
@@ -33855,7 +33856,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>77</v>
       </c>
@@ -33917,7 +33918,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>121</v>
       </c>
@@ -33982,7 +33983,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>122</v>
       </c>
@@ -34047,7 +34048,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>124</v>
       </c>
@@ -34112,7 +34113,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>125</v>
       </c>
@@ -34177,7 +34178,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>128</v>
       </c>
@@ -34242,7 +34243,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>172</v>
       </c>
@@ -34304,7 +34305,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>208</v>
       </c>
@@ -34369,7 +34370,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>214</v>
       </c>
@@ -34434,7 +34435,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>217</v>
       </c>
@@ -34499,7 +34500,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>218</v>
       </c>
@@ -34564,7 +34565,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>225</v>
       </c>
@@ -34629,7 +34630,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>239</v>
       </c>
@@ -34679,7 +34680,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>241</v>
       </c>
@@ -34741,7 +34742,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>434</v>
       </c>
@@ -34806,7 +34807,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>436</v>
       </c>
@@ -34871,7 +34872,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>485</v>
       </c>
@@ -34930,7 +34931,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>488</v>
       </c>
@@ -34992,7 +34993,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>509</v>
       </c>
@@ -35051,7 +35052,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>290</v>
       </c>
@@ -35116,7 +35117,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>77</v>
       </c>
@@ -35178,7 +35179,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>121</v>
       </c>
@@ -35243,7 +35244,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>122</v>
       </c>
@@ -35308,7 +35309,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>124</v>
       </c>
@@ -35373,7 +35374,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>125</v>
       </c>
@@ -35438,7 +35439,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>128</v>
       </c>
@@ -35503,7 +35504,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>172</v>
       </c>
@@ -35565,7 +35566,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>208</v>
       </c>
@@ -35630,7 +35631,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>214</v>
       </c>
@@ -35695,7 +35696,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>217</v>
       </c>
@@ -35760,7 +35761,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>218</v>
       </c>
@@ -35825,7 +35826,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>239</v>
       </c>
@@ -35875,7 +35876,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>434</v>
       </c>
@@ -35940,7 +35941,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>436</v>
       </c>
@@ -36005,7 +36006,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>485</v>
       </c>
@@ -36067,7 +36068,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>488</v>
       </c>
@@ -36129,7 +36130,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>290</v>
       </c>
@@ -36191,7 +36192,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>109</v>
       </c>
@@ -36253,7 +36254,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>112</v>
       </c>
@@ -36315,7 +36316,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>113</v>
       </c>
@@ -36377,7 +36378,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>114</v>
       </c>
@@ -36439,7 +36440,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>115</v>
       </c>
@@ -36501,7 +36502,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>117</v>
       </c>
@@ -36563,7 +36564,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>118</v>
       </c>
@@ -36625,7 +36626,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>133</v>
       </c>
@@ -36687,7 +36688,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>151</v>
       </c>
@@ -36749,7 +36750,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>77</v>
       </c>
@@ -36811,7 +36812,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>121</v>
       </c>
@@ -36876,7 +36877,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>122</v>
       </c>
@@ -36941,7 +36942,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>124</v>
       </c>
@@ -37006,7 +37007,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>125</v>
       </c>
@@ -37071,7 +37072,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>128</v>
       </c>
@@ -37136,7 +37137,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>172</v>
       </c>
@@ -37198,7 +37199,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>208</v>
       </c>
@@ -37263,7 +37264,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>214</v>
       </c>
@@ -37328,7 +37329,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>217</v>
       </c>
@@ -37387,7 +37388,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>218</v>
       </c>
@@ -37452,7 +37453,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>225</v>
       </c>
@@ -37514,7 +37515,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>239</v>
       </c>
@@ -37555,7 +37556,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>434</v>
       </c>
@@ -37620,7 +37621,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>436</v>
       </c>
@@ -37685,7 +37686,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>485</v>
       </c>
@@ -37747,7 +37748,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>488</v>
       </c>
@@ -37812,7 +37813,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>77</v>
       </c>
@@ -37874,7 +37875,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>121</v>
       </c>
@@ -37939,7 +37940,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>122</v>
       </c>
@@ -38004,7 +38005,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>124</v>
       </c>
@@ -38069,7 +38070,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>125</v>
       </c>
@@ -38134,7 +38135,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>128</v>
       </c>
@@ -38199,7 +38200,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>172</v>
       </c>
@@ -38261,7 +38262,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>208</v>
       </c>
@@ -38326,7 +38327,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>214</v>
       </c>
@@ -38391,7 +38392,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>217</v>
       </c>
@@ -38450,7 +38451,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>218</v>
       </c>
@@ -38515,7 +38516,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>225</v>
       </c>
@@ -38571,7 +38572,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>239</v>
       </c>
@@ -38612,7 +38613,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>434</v>
       </c>
@@ -38671,7 +38672,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>436</v>
       </c>
@@ -38736,7 +38737,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>485</v>
       </c>
@@ -38798,7 +38799,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>488</v>
       </c>
@@ -38863,7 +38864,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>73</v>
       </c>
@@ -38925,7 +38926,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>74</v>
       </c>
@@ -38987,7 +38988,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>86</v>
       </c>
@@ -39049,7 +39050,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>95</v>
       </c>
@@ -39111,7 +39112,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>143</v>
       </c>
@@ -39173,7 +39174,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>145</v>
       </c>
@@ -39235,7 +39236,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>146</v>
       </c>
@@ -39297,7 +39298,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>148</v>
       </c>
@@ -39359,7 +39360,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>159</v>
       </c>
@@ -39421,7 +39422,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>167</v>
       </c>
@@ -39483,7 +39484,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>193</v>
       </c>
@@ -39545,7 +39546,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>199</v>
       </c>
@@ -39607,7 +39608,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>203</v>
       </c>
@@ -39672,7 +39673,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>204</v>
       </c>
@@ -39737,7 +39738,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>205</v>
       </c>
@@ -39799,7 +39800,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>207</v>
       </c>
@@ -39864,7 +39865,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>219</v>
       </c>
@@ -39929,7 +39930,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>220</v>
       </c>
@@ -39994,7 +39995,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>245</v>
       </c>
@@ -40056,7 +40057,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>246</v>
       </c>
@@ -40118,7 +40119,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>252</v>
       </c>
@@ -40180,7 +40181,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>260</v>
       </c>
@@ -40245,7 +40246,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>261</v>
       </c>
@@ -40310,7 +40311,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>262</v>
       </c>
@@ -40360,7 +40361,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>268</v>
       </c>
@@ -40410,7 +40411,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>269</v>
       </c>
@@ -40460,7 +40461,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>270</v>
       </c>
@@ -40510,7 +40511,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>271</v>
       </c>
@@ -40560,7 +40561,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>273</v>
       </c>
@@ -40625,7 +40626,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>274</v>
       </c>
@@ -40687,7 +40688,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>275</v>
       </c>
@@ -40749,7 +40750,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>276</v>
       </c>
@@ -40814,7 +40815,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>277</v>
       </c>
@@ -40879,7 +40880,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>278</v>
       </c>
@@ -40929,7 +40930,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>282</v>
       </c>
@@ -40991,7 +40992,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>283</v>
       </c>
@@ -41053,7 +41054,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>285</v>
       </c>
@@ -41115,7 +41116,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>286</v>
       </c>
@@ -41165,7 +41166,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>292</v>
       </c>
@@ -41224,7 +41225,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>294</v>
       </c>
@@ -41283,7 +41284,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>302</v>
       </c>
@@ -41333,7 +41334,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>303</v>
       </c>
@@ -41395,7 +41396,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>304</v>
       </c>
@@ -41457,7 +41458,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>323</v>
       </c>
@@ -41519,7 +41520,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>324</v>
       </c>
@@ -41581,7 +41582,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>325</v>
       </c>
@@ -41631,7 +41632,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>327</v>
       </c>
@@ -41693,7 +41694,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>332</v>
       </c>
@@ -41758,7 +41759,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>337</v>
       </c>
@@ -41820,7 +41821,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>338</v>
       </c>
@@ -41882,7 +41883,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>341</v>
       </c>
@@ -41944,7 +41945,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>344</v>
       </c>
@@ -42006,7 +42007,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>356</v>
       </c>
@@ -42068,7 +42069,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>358</v>
       </c>
@@ -42130,7 +42131,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>359</v>
       </c>
@@ -42192,7 +42193,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>362</v>
       </c>
@@ -42254,7 +42255,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>363</v>
       </c>
@@ -42316,7 +42317,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>364</v>
       </c>
@@ -42378,7 +42379,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>369</v>
       </c>
@@ -42440,7 +42441,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>371</v>
       </c>
@@ -42502,7 +42503,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>375</v>
       </c>
@@ -42564,7 +42565,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>376</v>
       </c>
@@ -42629,7 +42630,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>379</v>
       </c>
@@ -42691,7 +42692,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>381</v>
       </c>
@@ -42756,7 +42757,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>382</v>
       </c>
@@ -42821,7 +42822,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>383</v>
       </c>
@@ -42886,7 +42887,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>384</v>
       </c>
@@ -42951,7 +42952,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>385</v>
       </c>
@@ -43016,7 +43017,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>386</v>
       </c>
@@ -43081,7 +43082,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>389</v>
       </c>
@@ -43122,7 +43123,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>397</v>
       </c>
@@ -43184,7 +43185,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>398</v>
       </c>
@@ -43246,7 +43247,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>399</v>
       </c>
@@ -43308,7 +43309,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>400</v>
       </c>
@@ -43370,7 +43371,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>401</v>
       </c>
@@ -43432,7 +43433,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>403</v>
       </c>
@@ -43482,7 +43483,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>408</v>
       </c>
@@ -43544,7 +43545,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>422</v>
       </c>
@@ -43606,7 +43607,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>427</v>
       </c>
@@ -43671,7 +43672,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>428</v>
       </c>
@@ -43736,7 +43737,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>429</v>
       </c>
@@ -43792,7 +43793,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>430</v>
       </c>
@@ -43857,7 +43858,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>433</v>
       </c>
@@ -43922,7 +43923,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>435</v>
       </c>
@@ -43987,7 +43988,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>439</v>
       </c>
@@ -44049,7 +44050,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>440</v>
       </c>
@@ -44111,7 +44112,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>444</v>
       </c>
@@ -44176,7 +44177,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>445</v>
       </c>
@@ -44238,7 +44239,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>447</v>
       </c>
@@ -44300,7 +44301,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>448</v>
       </c>
@@ -44362,7 +44363,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>451</v>
       </c>
@@ -44424,7 +44425,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>452</v>
       </c>
@@ -44480,7 +44481,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>466</v>
       </c>
@@ -44542,7 +44543,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>467</v>
       </c>
@@ -44604,7 +44605,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>468</v>
       </c>
@@ -44731,7 +44732,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>474</v>
       </c>
@@ -44772,7 +44773,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>475</v>
       </c>
@@ -44896,7 +44897,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>478</v>
       </c>
@@ -45055,7 +45056,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>506</v>
       </c>
@@ -45117,7 +45118,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>507</v>
       </c>
@@ -45179,7 +45180,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>514</v>
       </c>
@@ -45241,7 +45242,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>515</v>
       </c>
@@ -45294,7 +45295,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>516</v>
       </c>
@@ -45347,7 +45348,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>519</v>
       </c>
@@ -45409,7 +45410,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>523</v>
       </c>
@@ -45471,7 +45472,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>524</v>
       </c>
@@ -45533,7 +45534,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>532</v>
       </c>
@@ -45595,7 +45596,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>533</v>
       </c>
@@ -45657,7 +45658,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>534</v>
       </c>
@@ -45719,7 +45720,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -45781,7 +45782,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>536</v>
       </c>
@@ -45843,7 +45844,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>537</v>
       </c>
@@ -45905,7 +45906,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>538</v>
       </c>
@@ -45967,7 +45968,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>539</v>
       </c>
@@ -46029,7 +46030,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>540</v>
       </c>
@@ -46091,7 +46092,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>544</v>
       </c>
@@ -46153,7 +46154,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>550</v>
       </c>
@@ -46215,7 +46216,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>551</v>
       </c>
@@ -46277,7 +46278,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>554</v>
       </c>
@@ -46339,7 +46340,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>290</v>
       </c>
@@ -46404,7 +46405,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>69</v>
       </c>
@@ -46469,7 +46470,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>111</v>
       </c>
@@ -46531,7 +46532,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>197</v>
       </c>
@@ -46593,7 +46594,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>213</v>
       </c>
@@ -46649,7 +46650,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>251</v>
       </c>
@@ -46711,7 +46712,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>263</v>
       </c>
@@ -46773,7 +46774,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>300</v>
       </c>
@@ -46838,7 +46839,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>301</v>
       </c>
@@ -46903,7 +46904,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>306</v>
       </c>
@@ -46959,7 +46960,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>347</v>
       </c>
@@ -47024,7 +47025,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>348</v>
       </c>
@@ -47086,7 +47087,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>368</v>
       </c>
@@ -47148,7 +47149,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>372</v>
       </c>
@@ -47210,7 +47211,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>373</v>
       </c>
@@ -47263,7 +47264,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>390</v>
       </c>
@@ -47319,7 +47320,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>394</v>
       </c>
@@ -47381,7 +47382,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>395</v>
       </c>
@@ -47443,7 +47444,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>414</v>
       </c>
@@ -47496,7 +47497,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>415</v>
       </c>
@@ -47549,7 +47550,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>416</v>
       </c>
@@ -47602,7 +47603,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>417</v>
       </c>
@@ -47655,7 +47656,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>418</v>
       </c>
@@ -47708,7 +47709,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>420</v>
       </c>
@@ -47761,7 +47762,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>431</v>
       </c>
@@ -47823,7 +47824,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>432</v>
       </c>
@@ -47885,7 +47886,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>453</v>
       </c>
@@ -47947,7 +47948,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>455</v>
       </c>
@@ -48009,7 +48010,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>456</v>
       </c>
@@ -48062,7 +48063,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>457</v>
       </c>
@@ -48115,7 +48116,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>469</v>
       </c>
@@ -48168,7 +48169,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>470</v>
       </c>
@@ -48221,7 +48222,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>471</v>
       </c>
@@ -48274,7 +48275,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>484</v>
       </c>
@@ -48336,7 +48337,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>510</v>
       </c>
@@ -48386,7 +48387,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>511</v>
       </c>
@@ -48436,7 +48437,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>513</v>
       </c>
@@ -48483,7 +48484,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>513</v>
       </c>
@@ -48530,7 +48531,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>518</v>
       </c>
@@ -48592,7 +48593,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>84</v>
       </c>
@@ -48654,7 +48655,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>85</v>
       </c>
@@ -48716,7 +48717,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>87</v>
       </c>
@@ -48778,7 +48779,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>88</v>
       </c>
@@ -48840,7 +48841,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>89</v>
       </c>
@@ -48902,7 +48903,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>90</v>
       </c>
@@ -48964,7 +48965,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>91</v>
       </c>
@@ -49026,7 +49027,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>92</v>
       </c>
@@ -49091,7 +49092,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>94</v>
       </c>
@@ -49153,7 +49154,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>100</v>
       </c>
@@ -49215,7 +49216,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>104</v>
       </c>
@@ -49280,7 +49281,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>106</v>
       </c>
@@ -49342,7 +49343,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>116</v>
       </c>
@@ -49407,7 +49408,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>126</v>
       </c>
@@ -49469,7 +49470,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>127</v>
       </c>
@@ -49531,7 +49532,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>144</v>
       </c>
@@ -49593,7 +49594,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>147</v>
       </c>
@@ -49655,7 +49656,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>200</v>
       </c>
@@ -49717,7 +49718,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>202</v>
       </c>
@@ -49779,7 +49780,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>206</v>
       </c>
@@ -49841,7 +49842,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>216</v>
       </c>
@@ -49906,7 +49907,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>221</v>
       </c>
@@ -49962,7 +49963,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>222</v>
       </c>
@@ -50018,7 +50019,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>226</v>
       </c>
@@ -50074,7 +50075,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>227</v>
       </c>
@@ -50130,7 +50131,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>255</v>
       </c>
@@ -50174,7 +50175,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>272</v>
       </c>
@@ -50239,7 +50240,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>318</v>
       </c>
@@ -50301,7 +50302,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>326</v>
       </c>
@@ -50351,7 +50352,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>334</v>
       </c>
@@ -50413,7 +50414,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>336</v>
       </c>
@@ -50463,7 +50464,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>339</v>
       </c>
@@ -50525,7 +50526,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>346</v>
       </c>
@@ -50587,7 +50588,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>355</v>
       </c>
@@ -50634,7 +50635,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>361</v>
       </c>
@@ -50696,7 +50697,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>366</v>
       </c>
@@ -50758,7 +50759,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>367</v>
       </c>
@@ -50820,7 +50821,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>377</v>
       </c>
@@ -50882,7 +50883,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>392</v>
       </c>
@@ -50944,7 +50945,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>393</v>
       </c>
@@ -50994,7 +50995,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>402</v>
       </c>
@@ -51044,7 +51045,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>413</v>
       </c>
@@ -51100,7 +51101,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>423</v>
       </c>
@@ -51162,7 +51163,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>424</v>
       </c>
@@ -51224,7 +51225,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>437</v>
       </c>
@@ -51286,7 +51287,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>460</v>
       </c>
@@ -51348,7 +51349,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>487</v>
       </c>
@@ -51410,7 +51411,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>490</v>
       </c>
@@ -51472,7 +51473,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>491</v>
       </c>
@@ -51534,7 +51535,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>492</v>
       </c>
@@ -51596,7 +51597,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>493</v>
       </c>
@@ -51658,7 +51659,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>494</v>
       </c>
@@ -51720,7 +51721,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>495</v>
       </c>
@@ -51782,7 +51783,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>496</v>
       </c>
@@ -51844,7 +51845,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>498</v>
       </c>
@@ -51906,7 +51907,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>500</v>
       </c>
@@ -52030,7 +52031,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>502</v>
       </c>
@@ -52092,7 +52093,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>503</v>
       </c>
@@ -52154,7 +52155,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>504</v>
       </c>
@@ -52216,7 +52217,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>505</v>
       </c>
@@ -52278,7 +52279,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>508</v>
       </c>
@@ -52390,7 +52391,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>528</v>
       </c>
@@ -52446,7 +52447,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>541</v>
       </c>
@@ -52508,7 +52509,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>542</v>
       </c>
@@ -52558,7 +52559,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>546</v>
       </c>
@@ -52611,7 +52612,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>547</v>
       </c>
@@ -52661,7 +52662,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>553</v>
       </c>
@@ -52723,7 +52724,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>556</v>
       </c>
@@ -52786,6 +52787,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Y696" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Gestión, Evaluación e Innovación Curricular"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw/indicadores_kawak.xlsx
+++ b/data/raw/indicadores_kawak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{755A2398-2785-499A-B1D4-49013237F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA912791-97B7-4995-B1A7-F6B56D77DD81}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{755A2398-2785-499A-B1D4-49013237F3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9BC320A-08A0-493A-B379-7D4583CC50E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10248,7 +10248,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y696"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -10329,7 +10328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>77</v>
       </c>
@@ -10391,7 +10390,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>121</v>
       </c>
@@ -10453,7 +10452,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>122</v>
       </c>
@@ -10518,7 +10517,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>124</v>
       </c>
@@ -10583,7 +10582,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>125</v>
       </c>
@@ -10648,7 +10647,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>128</v>
       </c>
@@ -10713,7 +10712,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>172</v>
       </c>
@@ -10775,7 +10774,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>208</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>214</v>
       </c>
@@ -10887,7 +10886,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>218</v>
       </c>
@@ -10943,7 +10942,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>225</v>
       </c>
@@ -10999,7 +10998,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>239</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>436</v>
       </c>
@@ -11105,7 +11104,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>488</v>
       </c>
@@ -11155,7 +11154,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>77</v>
       </c>
@@ -11217,7 +11216,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>121</v>
       </c>
@@ -11282,7 +11281,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>122</v>
       </c>
@@ -11344,7 +11343,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>124</v>
       </c>
@@ -11409,7 +11408,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>125</v>
       </c>
@@ -11474,7 +11473,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>128</v>
       </c>
@@ -11539,7 +11538,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>172</v>
       </c>
@@ -11601,7 +11600,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>208</v>
       </c>
@@ -11666,7 +11665,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>214</v>
       </c>
@@ -11731,7 +11730,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>217</v>
       </c>
@@ -11796,7 +11795,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>218</v>
       </c>
@@ -11861,7 +11860,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>225</v>
       </c>
@@ -11926,7 +11925,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>239</v>
       </c>
@@ -11973,7 +11972,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>241</v>
       </c>
@@ -12035,7 +12034,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>434</v>
       </c>
@@ -12100,7 +12099,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>436</v>
       </c>
@@ -12165,7 +12164,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>485</v>
       </c>
@@ -12227,7 +12226,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>488</v>
       </c>
@@ -12292,7 +12291,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>509</v>
       </c>
@@ -12351,7 +12350,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>77</v>
       </c>
@@ -12413,7 +12412,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>121</v>
       </c>
@@ -12478,7 +12477,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>122</v>
       </c>
@@ -12543,7 +12542,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>124</v>
       </c>
@@ -12608,7 +12607,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>125</v>
       </c>
@@ -12673,7 +12672,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>128</v>
       </c>
@@ -12738,7 +12737,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>172</v>
       </c>
@@ -12797,7 +12796,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>208</v>
       </c>
@@ -12862,7 +12861,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>214</v>
       </c>
@@ -12927,7 +12926,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>217</v>
       </c>
@@ -12992,7 +12991,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>218</v>
       </c>
@@ -13057,7 +13056,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>225</v>
       </c>
@@ -13122,7 +13121,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>239</v>
       </c>
@@ -13169,7 +13168,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>241</v>
       </c>
@@ -13231,7 +13230,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>434</v>
       </c>
@@ -13296,7 +13295,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>436</v>
       </c>
@@ -13361,7 +13360,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>485</v>
       </c>
@@ -13423,7 +13422,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>488</v>
       </c>
@@ -13488,7 +13487,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>509</v>
       </c>
@@ -13544,7 +13543,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>290</v>
       </c>
@@ -13609,7 +13608,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>529</v>
       </c>
@@ -13653,7 +13652,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>77</v>
       </c>
@@ -13715,7 +13714,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>121</v>
       </c>
@@ -13780,7 +13779,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>122</v>
       </c>
@@ -13842,7 +13841,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>124</v>
       </c>
@@ -13907,7 +13906,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>125</v>
       </c>
@@ -13972,7 +13971,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>128</v>
       </c>
@@ -14037,7 +14036,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>172</v>
       </c>
@@ -14099,7 +14098,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>208</v>
       </c>
@@ -14164,7 +14163,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>214</v>
       </c>
@@ -14229,7 +14228,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>217</v>
       </c>
@@ -14294,7 +14293,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>218</v>
       </c>
@@ -14359,7 +14358,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>225</v>
       </c>
@@ -14424,7 +14423,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>239</v>
       </c>
@@ -14474,7 +14473,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>241</v>
       </c>
@@ -14536,7 +14535,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>434</v>
       </c>
@@ -14601,7 +14600,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>436</v>
       </c>
@@ -14666,7 +14665,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>485</v>
       </c>
@@ -14728,7 +14727,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>488</v>
       </c>
@@ -14790,7 +14789,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>509</v>
       </c>
@@ -14846,7 +14845,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>69</v>
       </c>
@@ -14911,7 +14910,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>111</v>
       </c>
@@ -14973,7 +14972,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>197</v>
       </c>
@@ -15035,7 +15034,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>213</v>
       </c>
@@ -15100,7 +15099,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>233</v>
       </c>
@@ -15162,7 +15161,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>234</v>
       </c>
@@ -15224,7 +15223,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>238</v>
       </c>
@@ -15289,7 +15288,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>240</v>
       </c>
@@ -15351,7 +15350,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>251</v>
       </c>
@@ -15413,7 +15412,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>254</v>
       </c>
@@ -15475,7 +15474,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>263</v>
       </c>
@@ -15537,7 +15536,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>265</v>
       </c>
@@ -15599,7 +15598,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>266</v>
       </c>
@@ -15661,7 +15660,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>300</v>
       </c>
@@ -15726,7 +15725,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>301</v>
       </c>
@@ -15791,7 +15790,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>306</v>
       </c>
@@ -15853,7 +15852,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>347</v>
       </c>
@@ -15918,7 +15917,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>348</v>
       </c>
@@ -15980,7 +15979,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>351</v>
       </c>
@@ -16045,7 +16044,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>352</v>
       </c>
@@ -16110,7 +16109,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>368</v>
       </c>
@@ -16172,7 +16171,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>372</v>
       </c>
@@ -16234,7 +16233,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>373</v>
       </c>
@@ -16293,7 +16292,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>390</v>
       </c>
@@ -16358,7 +16357,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>394</v>
       </c>
@@ -16420,7 +16419,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>395</v>
       </c>
@@ -16482,7 +16481,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>409</v>
       </c>
@@ -16544,7 +16543,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>414</v>
       </c>
@@ -16606,7 +16605,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>415</v>
       </c>
@@ -16668,7 +16667,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>416</v>
       </c>
@@ -16730,7 +16729,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>417</v>
       </c>
@@ -16792,7 +16791,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>418</v>
       </c>
@@ -16851,7 +16850,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>420</v>
       </c>
@@ -16910,7 +16909,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>431</v>
       </c>
@@ -16972,7 +16971,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>432</v>
       </c>
@@ -17031,7 +17030,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>453</v>
       </c>
@@ -17093,7 +17092,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>455</v>
       </c>
@@ -17155,7 +17154,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>456</v>
       </c>
@@ -17217,7 +17216,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>457</v>
       </c>
@@ -17279,7 +17278,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>469</v>
       </c>
@@ -17341,7 +17340,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>470</v>
       </c>
@@ -17403,7 +17402,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>471</v>
       </c>
@@ -17465,7 +17464,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>484</v>
       </c>
@@ -17527,7 +17526,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>510</v>
       </c>
@@ -17577,7 +17576,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>511</v>
       </c>
@@ -17627,7 +17626,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>513</v>
       </c>
@@ -17677,7 +17676,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>518</v>
       </c>
@@ -17739,7 +17738,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>529</v>
       </c>
@@ -17783,7 +17782,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>77</v>
       </c>
@@ -17845,7 +17844,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>121</v>
       </c>
@@ -17910,7 +17909,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>122</v>
       </c>
@@ -17975,7 +17974,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>124</v>
       </c>
@@ -18040,7 +18039,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>125</v>
       </c>
@@ -18105,7 +18104,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>128</v>
       </c>
@@ -18170,7 +18169,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>172</v>
       </c>
@@ -18232,7 +18231,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>208</v>
       </c>
@@ -18297,7 +18296,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>214</v>
       </c>
@@ -18362,7 +18361,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>217</v>
       </c>
@@ -18427,7 +18426,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>218</v>
       </c>
@@ -18492,7 +18491,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>225</v>
       </c>
@@ -18557,7 +18556,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>239</v>
       </c>
@@ -18607,7 +18606,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>241</v>
       </c>
@@ -18669,7 +18668,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>434</v>
       </c>
@@ -18734,7 +18733,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>436</v>
       </c>
@@ -18799,7 +18798,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>485</v>
       </c>
@@ -18861,7 +18860,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>488</v>
       </c>
@@ -18926,7 +18925,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>509</v>
       </c>
@@ -18982,7 +18981,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>290</v>
       </c>
@@ -19047,7 +19046,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>529</v>
       </c>
@@ -19091,7 +19090,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>77</v>
       </c>
@@ -19153,7 +19152,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>121</v>
       </c>
@@ -19218,7 +19217,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>122</v>
       </c>
@@ -19280,7 +19279,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>124</v>
       </c>
@@ -19345,7 +19344,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>125</v>
       </c>
@@ -19410,7 +19409,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>128</v>
       </c>
@@ -19475,7 +19474,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>172</v>
       </c>
@@ -19537,7 +19536,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>208</v>
       </c>
@@ -19602,7 +19601,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>214</v>
       </c>
@@ -19667,7 +19666,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>217</v>
       </c>
@@ -19732,7 +19731,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>218</v>
       </c>
@@ -19797,7 +19796,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>225</v>
       </c>
@@ -19862,7 +19861,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>239</v>
       </c>
@@ -19912,7 +19911,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>241</v>
       </c>
@@ -19974,7 +19973,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>434</v>
       </c>
@@ -20039,7 +20038,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>436</v>
       </c>
@@ -20104,7 +20103,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>485</v>
       </c>
@@ -20166,7 +20165,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>488</v>
       </c>
@@ -20231,7 +20230,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>509</v>
       </c>
@@ -20287,7 +20286,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>77</v>
       </c>
@@ -20349,7 +20348,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>121</v>
       </c>
@@ -20414,7 +20413,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>122</v>
       </c>
@@ -20479,7 +20478,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>124</v>
       </c>
@@ -20544,7 +20543,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>125</v>
       </c>
@@ -20609,7 +20608,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>128</v>
       </c>
@@ -20674,7 +20673,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>172</v>
       </c>
@@ -20736,7 +20735,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>208</v>
       </c>
@@ -20801,7 +20800,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -20866,7 +20865,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>217</v>
       </c>
@@ -20931,7 +20930,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>218</v>
       </c>
@@ -20996,7 +20995,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>225</v>
       </c>
@@ -21061,7 +21060,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>239</v>
       </c>
@@ -21111,7 +21110,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>241</v>
       </c>
@@ -21173,7 +21172,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>434</v>
       </c>
@@ -21238,7 +21237,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>436</v>
       </c>
@@ -21303,7 +21302,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>485</v>
       </c>
@@ -21365,7 +21364,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>488</v>
       </c>
@@ -21430,7 +21429,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>509</v>
       </c>
@@ -21489,7 +21488,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>68</v>
       </c>
@@ -21554,7 +21553,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>73</v>
       </c>
@@ -21616,7 +21615,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>74</v>
       </c>
@@ -21678,7 +21677,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>86</v>
       </c>
@@ -21740,7 +21739,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>95</v>
       </c>
@@ -21802,7 +21801,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>143</v>
       </c>
@@ -21864,7 +21863,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>145</v>
       </c>
@@ -21926,7 +21925,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>146</v>
       </c>
@@ -21988,7 +21987,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>148</v>
       </c>
@@ -22050,7 +22049,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>159</v>
       </c>
@@ -22112,7 +22111,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>167</v>
       </c>
@@ -22174,7 +22173,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>193</v>
       </c>
@@ -22236,7 +22235,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>199</v>
       </c>
@@ -22298,7 +22297,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>203</v>
       </c>
@@ -22363,7 +22362,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>204</v>
       </c>
@@ -22428,7 +22427,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>205</v>
       </c>
@@ -22490,7 +22489,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>207</v>
       </c>
@@ -22555,7 +22554,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>215</v>
       </c>
@@ -22620,7 +22619,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>219</v>
       </c>
@@ -22685,7 +22684,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>220</v>
       </c>
@@ -22750,7 +22749,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>230</v>
       </c>
@@ -22815,7 +22814,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>231</v>
       </c>
@@ -22877,7 +22876,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>232</v>
       </c>
@@ -22939,7 +22938,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>245</v>
       </c>
@@ -23001,7 +23000,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>246</v>
       </c>
@@ -23063,7 +23062,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>252</v>
       </c>
@@ -23125,7 +23124,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>256</v>
       </c>
@@ -23187,7 +23186,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>260</v>
       </c>
@@ -23252,7 +23251,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>261</v>
       </c>
@@ -23317,7 +23316,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>262</v>
       </c>
@@ -23382,7 +23381,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>268</v>
       </c>
@@ -23432,7 +23431,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>269</v>
       </c>
@@ -23482,7 +23481,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>270</v>
       </c>
@@ -23532,7 +23531,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>271</v>
       </c>
@@ -23582,7 +23581,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>273</v>
       </c>
@@ -23647,7 +23646,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>274</v>
       </c>
@@ -23709,7 +23708,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>275</v>
       </c>
@@ -23771,7 +23770,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>276</v>
       </c>
@@ -23836,7 +23835,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>277</v>
       </c>
@@ -23901,7 +23900,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>278</v>
       </c>
@@ -23951,7 +23950,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>282</v>
       </c>
@@ -24013,7 +24012,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>283</v>
       </c>
@@ -24075,7 +24074,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>285</v>
       </c>
@@ -24137,7 +24136,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>286</v>
       </c>
@@ -24187,7 +24186,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>292</v>
       </c>
@@ -24249,7 +24248,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>294</v>
       </c>
@@ -24311,7 +24310,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>302</v>
       </c>
@@ -24361,7 +24360,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>303</v>
       </c>
@@ -24423,7 +24422,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>304</v>
       </c>
@@ -24485,7 +24484,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>323</v>
       </c>
@@ -24547,7 +24546,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>324</v>
       </c>
@@ -24609,7 +24608,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>325</v>
       </c>
@@ -24659,7 +24658,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>327</v>
       </c>
@@ -24721,7 +24720,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>332</v>
       </c>
@@ -24786,7 +24785,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>337</v>
       </c>
@@ -24848,7 +24847,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>338</v>
       </c>
@@ -24910,7 +24909,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>341</v>
       </c>
@@ -24972,7 +24971,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>344</v>
       </c>
@@ -25034,7 +25033,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>356</v>
       </c>
@@ -25099,7 +25098,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>357</v>
       </c>
@@ -25149,7 +25148,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>358</v>
       </c>
@@ -25211,7 +25210,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>359</v>
       </c>
@@ -25273,7 +25272,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>362</v>
       </c>
@@ -25335,7 +25334,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>363</v>
       </c>
@@ -25397,7 +25396,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>364</v>
       </c>
@@ -25459,7 +25458,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>369</v>
       </c>
@@ -25521,7 +25520,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>371</v>
       </c>
@@ -25583,7 +25582,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>375</v>
       </c>
@@ -25645,7 +25644,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>376</v>
       </c>
@@ -25710,7 +25709,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>379</v>
       </c>
@@ -25772,7 +25771,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>381</v>
       </c>
@@ -25837,7 +25836,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>382</v>
       </c>
@@ -25902,7 +25901,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>383</v>
       </c>
@@ -25967,7 +25966,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>384</v>
       </c>
@@ -26032,7 +26031,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>385</v>
       </c>
@@ -26097,7 +26096,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>386</v>
       </c>
@@ -26162,7 +26161,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>389</v>
       </c>
@@ -26206,7 +26205,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>397</v>
       </c>
@@ -26268,7 +26267,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>398</v>
       </c>
@@ -26330,7 +26329,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>399</v>
       </c>
@@ -26392,7 +26391,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>400</v>
       </c>
@@ -26454,7 +26453,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>401</v>
       </c>
@@ -26516,7 +26515,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>403</v>
       </c>
@@ -26566,7 +26565,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>408</v>
       </c>
@@ -26628,7 +26627,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>422</v>
       </c>
@@ -26690,7 +26689,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>427</v>
       </c>
@@ -26755,7 +26754,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>428</v>
       </c>
@@ -26820,7 +26819,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>429</v>
       </c>
@@ -26885,7 +26884,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>430</v>
       </c>
@@ -26950,7 +26949,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>433</v>
       </c>
@@ -27015,7 +27014,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>435</v>
       </c>
@@ -27080,7 +27079,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>439</v>
       </c>
@@ -27142,7 +27141,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>440</v>
       </c>
@@ -27204,7 +27203,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>444</v>
       </c>
@@ -27269,7 +27268,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>445</v>
       </c>
@@ -27331,7 +27330,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>447</v>
       </c>
@@ -27393,7 +27392,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>448</v>
       </c>
@@ -27455,7 +27454,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>451</v>
       </c>
@@ -27517,7 +27516,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>452</v>
       </c>
@@ -27573,7 +27572,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>466</v>
       </c>
@@ -27635,7 +27634,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>467</v>
       </c>
@@ -27697,7 +27696,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>468</v>
       </c>
@@ -27824,7 +27823,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>474</v>
       </c>
@@ -27868,7 +27867,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>475</v>
       </c>
@@ -27992,7 +27991,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>477</v>
       </c>
@@ -28033,7 +28032,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>478</v>
       </c>
@@ -28077,7 +28076,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>479</v>
       </c>
@@ -28130,7 +28129,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>480</v>
       </c>
@@ -28239,7 +28238,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>486</v>
       </c>
@@ -28289,7 +28288,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>506</v>
       </c>
@@ -28351,7 +28350,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>507</v>
       </c>
@@ -28413,7 +28412,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>514</v>
       </c>
@@ -28475,7 +28474,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>519</v>
       </c>
@@ -28537,7 +28536,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>523</v>
       </c>
@@ -28602,7 +28601,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>524</v>
       </c>
@@ -28664,7 +28663,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>532</v>
       </c>
@@ -28726,7 +28725,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>533</v>
       </c>
@@ -28788,7 +28787,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>534</v>
       </c>
@@ -28850,7 +28849,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>535</v>
       </c>
@@ -28912,7 +28911,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>536</v>
       </c>
@@ -28974,7 +28973,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>537</v>
       </c>
@@ -29036,7 +29035,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>540</v>
       </c>
@@ -29098,7 +29097,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>543</v>
       </c>
@@ -29148,7 +29147,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>544</v>
       </c>
@@ -29210,7 +29209,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>550</v>
       </c>
@@ -29269,7 +29268,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>551</v>
       </c>
@@ -29328,7 +29327,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>552</v>
       </c>
@@ -29390,7 +29389,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>290</v>
       </c>
@@ -29455,7 +29454,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>69</v>
       </c>
@@ -29520,7 +29519,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>111</v>
       </c>
@@ -29582,7 +29581,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>197</v>
       </c>
@@ -29644,7 +29643,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>213</v>
       </c>
@@ -29709,7 +29708,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>233</v>
       </c>
@@ -29771,7 +29770,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>234</v>
       </c>
@@ -29833,7 +29832,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>238</v>
       </c>
@@ -29898,7 +29897,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>240</v>
       </c>
@@ -29960,7 +29959,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>251</v>
       </c>
@@ -30022,7 +30021,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>254</v>
       </c>
@@ -30084,7 +30083,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>263</v>
       </c>
@@ -30146,7 +30145,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>265</v>
       </c>
@@ -30208,7 +30207,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>266</v>
       </c>
@@ -30270,7 +30269,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>300</v>
       </c>
@@ -30335,7 +30334,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>301</v>
       </c>
@@ -30400,7 +30399,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>306</v>
       </c>
@@ -30465,7 +30464,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>347</v>
       </c>
@@ -30530,7 +30529,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>348</v>
       </c>
@@ -30592,7 +30591,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>351</v>
       </c>
@@ -30657,7 +30656,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>352</v>
       </c>
@@ -30722,7 +30721,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>368</v>
       </c>
@@ -30784,7 +30783,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>372</v>
       </c>
@@ -30846,7 +30845,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>373</v>
       </c>
@@ -30905,7 +30904,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>390</v>
       </c>
@@ -30967,7 +30966,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>394</v>
       </c>
@@ -31029,7 +31028,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>395</v>
       </c>
@@ -31091,7 +31090,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>409</v>
       </c>
@@ -31144,7 +31143,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>414</v>
       </c>
@@ -31203,7 +31202,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>415</v>
       </c>
@@ -31262,7 +31261,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>416</v>
       </c>
@@ -31321,7 +31320,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>417</v>
       </c>
@@ -31380,7 +31379,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>418</v>
       </c>
@@ -31439,7 +31438,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>420</v>
       </c>
@@ -31498,7 +31497,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>431</v>
       </c>
@@ -31560,7 +31559,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>432</v>
       </c>
@@ -31619,7 +31618,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>453</v>
       </c>
@@ -31681,7 +31680,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>455</v>
       </c>
@@ -31743,7 +31742,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>456</v>
       </c>
@@ -31805,7 +31804,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>457</v>
       </c>
@@ -31867,7 +31866,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>469</v>
       </c>
@@ -31926,7 +31925,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>470</v>
       </c>
@@ -31985,7 +31984,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>471</v>
       </c>
@@ -32044,7 +32043,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>484</v>
       </c>
@@ -32106,7 +32105,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>510</v>
       </c>
@@ -32156,7 +32155,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>511</v>
       </c>
@@ -32206,7 +32205,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>513</v>
       </c>
@@ -32256,7 +32255,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>518</v>
       </c>
@@ -32318,7 +32317,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>526</v>
       </c>
@@ -32380,7 +32379,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>526</v>
       </c>
@@ -32442,7 +32441,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>529</v>
       </c>
@@ -32486,7 +32485,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>529</v>
       </c>
@@ -32530,7 +32529,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>288</v>
       </c>
@@ -32592,7 +32591,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>528</v>
       </c>
@@ -32654,7 +32653,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>77</v>
       </c>
@@ -32716,7 +32715,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>121</v>
       </c>
@@ -32781,7 +32780,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>122</v>
       </c>
@@ -32846,7 +32845,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>124</v>
       </c>
@@ -32911,7 +32910,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>125</v>
       </c>
@@ -32976,7 +32975,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>128</v>
       </c>
@@ -33041,7 +33040,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>172</v>
       </c>
@@ -33103,7 +33102,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>208</v>
       </c>
@@ -33168,7 +33167,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>214</v>
       </c>
@@ -33233,7 +33232,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>217</v>
       </c>
@@ -33298,7 +33297,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>218</v>
       </c>
@@ -33363,7 +33362,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>225</v>
       </c>
@@ -33428,7 +33427,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>239</v>
       </c>
@@ -33478,7 +33477,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>241</v>
       </c>
@@ -33540,7 +33539,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>434</v>
       </c>
@@ -33605,7 +33604,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>436</v>
       </c>
@@ -33670,7 +33669,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>485</v>
       </c>
@@ -33732,7 +33731,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>488</v>
       </c>
@@ -33797,7 +33796,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>509</v>
       </c>
@@ -33856,7 +33855,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>77</v>
       </c>
@@ -33918,7 +33917,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>121</v>
       </c>
@@ -33983,7 +33982,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>122</v>
       </c>
@@ -34048,7 +34047,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>124</v>
       </c>
@@ -34113,7 +34112,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>125</v>
       </c>
@@ -34178,7 +34177,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>128</v>
       </c>
@@ -34243,7 +34242,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>172</v>
       </c>
@@ -34305,7 +34304,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>208</v>
       </c>
@@ -34370,7 +34369,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>214</v>
       </c>
@@ -34435,7 +34434,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>217</v>
       </c>
@@ -34500,7 +34499,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>218</v>
       </c>
@@ -34565,7 +34564,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>225</v>
       </c>
@@ -34630,7 +34629,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>239</v>
       </c>
@@ -34680,7 +34679,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>241</v>
       </c>
@@ -34742,7 +34741,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>434</v>
       </c>
@@ -34807,7 +34806,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>436</v>
       </c>
@@ -34872,7 +34871,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>485</v>
       </c>
@@ -34931,7 +34930,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>488</v>
       </c>
@@ -34993,7 +34992,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>509</v>
       </c>
@@ -35052,7 +35051,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>290</v>
       </c>
@@ -35117,7 +35116,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>77</v>
       </c>
@@ -35179,7 +35178,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>121</v>
       </c>
@@ -35244,7 +35243,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>122</v>
       </c>
@@ -35309,7 +35308,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>124</v>
       </c>
@@ -35374,7 +35373,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>125</v>
       </c>
@@ -35439,7 +35438,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>128</v>
       </c>
@@ -35504,7 +35503,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>172</v>
       </c>
@@ -35566,7 +35565,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>208</v>
       </c>
@@ -35631,7 +35630,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>214</v>
       </c>
@@ -35696,7 +35695,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>217</v>
       </c>
@@ -35761,7 +35760,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>218</v>
       </c>
@@ -35826,7 +35825,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>239</v>
       </c>
@@ -35876,7 +35875,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>434</v>
       </c>
@@ -35941,7 +35940,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>436</v>
       </c>
@@ -36006,7 +36005,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>485</v>
       </c>
@@ -36068,7 +36067,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>488</v>
       </c>
@@ -36130,7 +36129,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>290</v>
       </c>
@@ -36192,7 +36191,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>109</v>
       </c>
@@ -36254,7 +36253,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>112</v>
       </c>
@@ -36316,7 +36315,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>113</v>
       </c>
@@ -36378,7 +36377,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>114</v>
       </c>
@@ -36440,7 +36439,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>115</v>
       </c>
@@ -36502,7 +36501,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>117</v>
       </c>
@@ -36564,7 +36563,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>118</v>
       </c>
@@ -36626,7 +36625,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>133</v>
       </c>
@@ -36688,7 +36687,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>151</v>
       </c>
@@ -36750,7 +36749,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>77</v>
       </c>
@@ -36812,7 +36811,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>121</v>
       </c>
@@ -36877,7 +36876,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>122</v>
       </c>
@@ -36942,7 +36941,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>124</v>
       </c>
@@ -37007,7 +37006,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>125</v>
       </c>
@@ -37072,7 +37071,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>128</v>
       </c>
@@ -37137,7 +37136,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>172</v>
       </c>
@@ -37199,7 +37198,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>208</v>
       </c>
@@ -37264,7 +37263,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>214</v>
       </c>
@@ -37329,7 +37328,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>217</v>
       </c>
@@ -37388,7 +37387,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>218</v>
       </c>
@@ -37453,7 +37452,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>225</v>
       </c>
@@ -37515,7 +37514,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>239</v>
       </c>
@@ -37556,7 +37555,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>434</v>
       </c>
@@ -37621,7 +37620,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>436</v>
       </c>
@@ -37686,7 +37685,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>485</v>
       </c>
@@ -37748,7 +37747,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>488</v>
       </c>
@@ -37813,7 +37812,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>77</v>
       </c>
@@ -37875,7 +37874,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>121</v>
       </c>
@@ -37940,7 +37939,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>122</v>
       </c>
@@ -38005,7 +38004,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>124</v>
       </c>
@@ -38070,7 +38069,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>125</v>
       </c>
@@ -38135,7 +38134,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>128</v>
       </c>
@@ -38200,7 +38199,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>172</v>
       </c>
@@ -38262,7 +38261,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>208</v>
       </c>
@@ -38327,7 +38326,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>214</v>
       </c>
@@ -38392,7 +38391,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>217</v>
       </c>
@@ -38451,7 +38450,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>218</v>
       </c>
@@ -38516,7 +38515,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>225</v>
       </c>
@@ -38572,7 +38571,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>239</v>
       </c>
@@ -38613,7 +38612,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>434</v>
       </c>
@@ -38672,7 +38671,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>436</v>
       </c>
@@ -38737,7 +38736,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>485</v>
       </c>
@@ -38799,7 +38798,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>488</v>
       </c>
@@ -38864,7 +38863,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>73</v>
       </c>
@@ -38926,7 +38925,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>74</v>
       </c>
@@ -38988,7 +38987,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>86</v>
       </c>
@@ -39050,7 +39049,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>95</v>
       </c>
@@ -39112,7 +39111,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>143</v>
       </c>
@@ -39174,7 +39173,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>145</v>
       </c>
@@ -39236,7 +39235,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>146</v>
       </c>
@@ -39298,7 +39297,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>148</v>
       </c>
@@ -39360,7 +39359,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>159</v>
       </c>
@@ -39422,7 +39421,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>167</v>
       </c>
@@ -39484,7 +39483,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>193</v>
       </c>
@@ -39546,7 +39545,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>199</v>
       </c>
@@ -39608,7 +39607,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>203</v>
       </c>
@@ -39673,7 +39672,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>204</v>
       </c>
@@ -39738,7 +39737,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>205</v>
       </c>
@@ -39800,7 +39799,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>207</v>
       </c>
@@ -39865,7 +39864,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>219</v>
       </c>
@@ -39930,7 +39929,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>220</v>
       </c>
@@ -39995,7 +39994,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>245</v>
       </c>
@@ -40057,7 +40056,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>246</v>
       </c>
@@ -40119,7 +40118,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>252</v>
       </c>
@@ -40181,7 +40180,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>260</v>
       </c>
@@ -40246,7 +40245,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>261</v>
       </c>
@@ -40311,7 +40310,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>262</v>
       </c>
@@ -40361,7 +40360,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>268</v>
       </c>
@@ -40411,7 +40410,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>269</v>
       </c>
@@ -40461,7 +40460,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>270</v>
       </c>
@@ -40511,7 +40510,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>271</v>
       </c>
@@ -40561,7 +40560,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>273</v>
       </c>
@@ -40626,7 +40625,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>274</v>
       </c>
@@ -40688,7 +40687,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>275</v>
       </c>
@@ -40750,7 +40749,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>276</v>
       </c>
@@ -40815,7 +40814,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>277</v>
       </c>
@@ -40880,7 +40879,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>278</v>
       </c>
@@ -40930,7 +40929,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>282</v>
       </c>
@@ -40992,7 +40991,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>283</v>
       </c>
@@ -41054,7 +41053,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>285</v>
       </c>
@@ -41116,7 +41115,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>286</v>
       </c>
@@ -41166,7 +41165,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>292</v>
       </c>
@@ -41225,7 +41224,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>294</v>
       </c>
@@ -41284,7 +41283,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>302</v>
       </c>
@@ -41334,7 +41333,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>303</v>
       </c>
@@ -41396,7 +41395,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>304</v>
       </c>
@@ -41458,7 +41457,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>323</v>
       </c>
@@ -41520,7 +41519,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>324</v>
       </c>
@@ -41582,7 +41581,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>325</v>
       </c>
@@ -41632,7 +41631,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>327</v>
       </c>
@@ -41694,7 +41693,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>332</v>
       </c>
@@ -41759,7 +41758,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>337</v>
       </c>
@@ -41821,7 +41820,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>338</v>
       </c>
@@ -41883,7 +41882,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>341</v>
       </c>
@@ -41945,7 +41944,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>344</v>
       </c>
@@ -42007,7 +42006,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>356</v>
       </c>
@@ -42069,7 +42068,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>358</v>
       </c>
@@ -42131,7 +42130,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>359</v>
       </c>
@@ -42193,7 +42192,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>362</v>
       </c>
@@ -42255,7 +42254,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>363</v>
       </c>
@@ -42317,7 +42316,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>364</v>
       </c>
@@ -42379,7 +42378,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>369</v>
       </c>
@@ -42441,7 +42440,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>371</v>
       </c>
@@ -42503,7 +42502,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>375</v>
       </c>
@@ -42565,7 +42564,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>376</v>
       </c>
@@ -42630,7 +42629,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>379</v>
       </c>
@@ -42692,7 +42691,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>381</v>
       </c>
@@ -42757,7 +42756,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>382</v>
       </c>
@@ -42822,7 +42821,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>383</v>
       </c>
@@ -42887,7 +42886,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>384</v>
       </c>
@@ -42952,7 +42951,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>385</v>
       </c>
@@ -43017,7 +43016,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>386</v>
       </c>
@@ -43082,7 +43081,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>389</v>
       </c>
@@ -43123,7 +43122,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>397</v>
       </c>
@@ -43185,7 +43184,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>398</v>
       </c>
@@ -43247,7 +43246,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>399</v>
       </c>
@@ -43309,7 +43308,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>400</v>
       </c>
@@ -43371,7 +43370,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>401</v>
       </c>
@@ -43433,7 +43432,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>403</v>
       </c>
@@ -43483,7 +43482,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>408</v>
       </c>
@@ -43545,7 +43544,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>422</v>
       </c>
@@ -43607,7 +43606,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>427</v>
       </c>
@@ -43672,7 +43671,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>428</v>
       </c>
@@ -43737,7 +43736,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>429</v>
       </c>
@@ -43793,7 +43792,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>430</v>
       </c>
@@ -43858,7 +43857,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>433</v>
       </c>
@@ -43923,7 +43922,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>435</v>
       </c>
@@ -43988,7 +43987,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>439</v>
       </c>
@@ -44050,7 +44049,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>440</v>
       </c>
@@ -44112,7 +44111,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>444</v>
       </c>
@@ -44177,7 +44176,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>445</v>
       </c>
@@ -44239,7 +44238,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>447</v>
       </c>
@@ -44301,7 +44300,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>448</v>
       </c>
@@ -44363,7 +44362,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>451</v>
       </c>
@@ -44425,7 +44424,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>452</v>
       </c>
@@ -44481,7 +44480,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>466</v>
       </c>
@@ -44543,7 +44542,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>467</v>
       </c>
@@ -44605,7 +44604,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>468</v>
       </c>
@@ -44732,7 +44731,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>474</v>
       </c>
@@ -44773,7 +44772,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>475</v>
       </c>
@@ -44897,7 +44896,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>478</v>
       </c>
@@ -45056,7 +45055,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>506</v>
       </c>
@@ -45118,7 +45117,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>507</v>
       </c>
@@ -45180,7 +45179,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>514</v>
       </c>
@@ -45242,7 +45241,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>515</v>
       </c>
@@ -45295,7 +45294,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>516</v>
       </c>
@@ -45348,7 +45347,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>519</v>
       </c>
@@ -45410,7 +45409,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>523</v>
       </c>
@@ -45472,7 +45471,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>524</v>
       </c>
@@ -45534,7 +45533,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>532</v>
       </c>
@@ -45596,7 +45595,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>533</v>
       </c>
@@ -45658,7 +45657,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>534</v>
       </c>
@@ -45720,7 +45719,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -45782,7 +45781,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>536</v>
       </c>
@@ -45844,7 +45843,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>537</v>
       </c>
@@ -45906,7 +45905,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>538</v>
       </c>
@@ -45968,7 +45967,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>539</v>
       </c>
@@ -46030,7 +46029,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>540</v>
       </c>
@@ -46092,7 +46091,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>544</v>
       </c>
@@ -46154,7 +46153,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>550</v>
       </c>
@@ -46216,7 +46215,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>551</v>
       </c>
@@ -46278,7 +46277,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>554</v>
       </c>
@@ -46340,7 +46339,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>290</v>
       </c>
@@ -46405,7 +46404,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>69</v>
       </c>
@@ -46470,7 +46469,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>111</v>
       </c>
@@ -46532,7 +46531,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>197</v>
       </c>
@@ -46594,7 +46593,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>213</v>
       </c>
@@ -46650,7 +46649,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>251</v>
       </c>
@@ -46712,7 +46711,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>263</v>
       </c>
@@ -46774,7 +46773,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>300</v>
       </c>
@@ -46839,7 +46838,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>301</v>
       </c>
@@ -46904,7 +46903,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>306</v>
       </c>
@@ -46960,7 +46959,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>347</v>
       </c>
@@ -47025,7 +47024,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>348</v>
       </c>
@@ -47087,7 +47086,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>368</v>
       </c>
@@ -47149,7 +47148,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>372</v>
       </c>
@@ -47211,7 +47210,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>373</v>
       </c>
@@ -47264,7 +47263,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>390</v>
       </c>
@@ -47320,7 +47319,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>394</v>
       </c>
@@ -47382,7 +47381,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>395</v>
       </c>
@@ -47444,7 +47443,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>414</v>
       </c>
@@ -47497,7 +47496,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>415</v>
       </c>
@@ -47550,7 +47549,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>416</v>
       </c>
@@ -47603,7 +47602,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>417</v>
       </c>
@@ -47656,7 +47655,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>418</v>
       </c>
@@ -47709,7 +47708,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>420</v>
       </c>
@@ -47762,7 +47761,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>431</v>
       </c>
@@ -47824,7 +47823,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>432</v>
       </c>
@@ -47886,7 +47885,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>453</v>
       </c>
@@ -47948,7 +47947,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>455</v>
       </c>
@@ -48010,7 +48009,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>456</v>
       </c>
@@ -48063,7 +48062,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>457</v>
       </c>
@@ -48116,7 +48115,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>469</v>
       </c>
@@ -48169,7 +48168,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>470</v>
       </c>
@@ -48222,7 +48221,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>471</v>
       </c>
@@ -48275,7 +48274,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>484</v>
       </c>
@@ -48337,7 +48336,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>510</v>
       </c>
@@ -48387,7 +48386,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>511</v>
       </c>
@@ -48437,7 +48436,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>513</v>
       </c>
@@ -48484,7 +48483,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>513</v>
       </c>
@@ -48531,7 +48530,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>518</v>
       </c>
@@ -48593,7 +48592,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>84</v>
       </c>
@@ -48655,7 +48654,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>85</v>
       </c>
@@ -48717,7 +48716,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>87</v>
       </c>
@@ -48779,7 +48778,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>88</v>
       </c>
@@ -48841,7 +48840,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>89</v>
       </c>
@@ -48903,7 +48902,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>90</v>
       </c>
@@ -48965,7 +48964,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>91</v>
       </c>
@@ -49027,7 +49026,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>92</v>
       </c>
@@ -49092,7 +49091,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>94</v>
       </c>
@@ -49154,7 +49153,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>100</v>
       </c>
@@ -49216,7 +49215,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>104</v>
       </c>
@@ -49281,7 +49280,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>106</v>
       </c>
@@ -49343,7 +49342,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>116</v>
       </c>
@@ -49408,7 +49407,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>126</v>
       </c>
@@ -49470,7 +49469,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>127</v>
       </c>
@@ -49532,7 +49531,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>144</v>
       </c>
@@ -49594,7 +49593,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>147</v>
       </c>
@@ -49656,7 +49655,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>200</v>
       </c>
@@ -49718,7 +49717,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>202</v>
       </c>
@@ -49780,7 +49779,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>206</v>
       </c>
@@ -49842,7 +49841,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>216</v>
       </c>
@@ -49907,7 +49906,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>221</v>
       </c>
@@ -49963,7 +49962,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>222</v>
       </c>
@@ -50019,7 +50018,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>226</v>
       </c>
@@ -50075,7 +50074,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>227</v>
       </c>
@@ -50131,7 +50130,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>255</v>
       </c>
@@ -50175,7 +50174,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>272</v>
       </c>
@@ -50240,7 +50239,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>318</v>
       </c>
@@ -50302,7 +50301,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>326</v>
       </c>
@@ -50352,7 +50351,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>334</v>
       </c>
@@ -50414,7 +50413,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>336</v>
       </c>
@@ -50464,7 +50463,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>339</v>
       </c>
@@ -50526,7 +50525,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>346</v>
       </c>
@@ -50588,7 +50587,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>355</v>
       </c>
@@ -50635,7 +50634,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>361</v>
       </c>
@@ -50697,7 +50696,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>366</v>
       </c>
@@ -50759,7 +50758,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>367</v>
       </c>
@@ -50821,7 +50820,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>377</v>
       </c>
@@ -50883,7 +50882,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>392</v>
       </c>
@@ -50945,7 +50944,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>393</v>
       </c>
@@ -50995,7 +50994,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>402</v>
       </c>
@@ -51045,7 +51044,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>413</v>
       </c>
@@ -51101,7 +51100,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>423</v>
       </c>
@@ -51163,7 +51162,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>424</v>
       </c>
@@ -51225,7 +51224,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>437</v>
       </c>
@@ -51287,7 +51286,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>460</v>
       </c>
@@ -51349,7 +51348,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>487</v>
       </c>
@@ -51411,7 +51410,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>490</v>
       </c>
@@ -51473,7 +51472,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>491</v>
       </c>
@@ -51535,7 +51534,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>492</v>
       </c>
@@ -51597,7 +51596,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>493</v>
       </c>
@@ -51659,7 +51658,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>494</v>
       </c>
@@ -51721,7 +51720,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>495</v>
       </c>
@@ -51783,7 +51782,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>496</v>
       </c>
@@ -51845,7 +51844,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>498</v>
       </c>
@@ -51907,7 +51906,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>500</v>
       </c>
@@ -52031,7 +52030,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>502</v>
       </c>
@@ -52093,7 +52092,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>503</v>
       </c>
@@ -52155,7 +52154,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>504</v>
       </c>
@@ -52217,7 +52216,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>505</v>
       </c>
@@ -52279,7 +52278,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>508</v>
       </c>
@@ -52391,7 +52390,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>528</v>
       </c>
@@ -52447,7 +52446,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>541</v>
       </c>
@@ -52509,7 +52508,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>542</v>
       </c>
@@ -52559,7 +52558,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>546</v>
       </c>
@@ -52612,7 +52611,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>547</v>
       </c>
@@ -52662,7 +52661,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>553</v>
       </c>
@@ -52724,7 +52723,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>556</v>
       </c>
@@ -52787,13 +52786,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y696" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Gestión, Evaluación e Innovación Curricular"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>